--- a/site/public/ig/ValueSet-heartland-monitoring-track-vs.xlsx
+++ b/site/public/ig/ValueSet-heartland-monitoring-track-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T20:13:50-04:00</t>
+    <t>2026-09-17T14:02:25-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/ValueSet-heartland-monitoring-track-vs.xlsx
+++ b/site/public/ig/ValueSet-heartland-monitoring-track-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:02:25-04:00</t>
+    <t>2026-09-17T14:11:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/public/ig/ValueSet-heartland-monitoring-track-vs.xlsx
+++ b/site/public/ig/ValueSet-heartland-monitoring-track-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,19 +48,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T14:11:14-04:00</t>
+    <t>2026-09-29T19:00:36-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
